--- a/output/pdf_financials_xlsx/OGI.xlsx
+++ b/output/pdf_financials_xlsx/OGI.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.08081199999999999</v>
+        <v>-0.08081199999999999</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.140164</v>
+        <v>-0.140164</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.375245</v>
+        <v>-0.375245</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-8.269280999999999</v>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.08081199999999999</v>
+        <v>-0.08081199999999999</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.140164</v>
+        <v>-0.140164</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.375245</v>
+        <v>-0.375245</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-8.269280999999999</v>
@@ -1534,13 +1534,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.08081199999999999</v>
+        <v>-0.08081199999999999</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.140164</v>
+        <v>-0.140164</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.375245</v>
+        <v>-0.375245</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-8.269280999999999</v>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.475365</v>
+        <v>-0.475365</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>7.0082</v>
+        <v>-7.0082</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>7.5049</v>
+        <v>-7.5049</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>31.683069</v>
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.08081199999999999</v>
+        <v>-0.08081199999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.140164</v>
+        <v>-0.140164</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.375245</v>
+        <v>-0.375245</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-8.269280999999999</v>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.08081199999999999</v>
+        <v>-0.08081199999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.140164</v>
+        <v>-0.140164</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.375245</v>
+        <v>-0.375245</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-8.217283999999999</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -6337,13 +6337,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -45514,7 +45514,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E449" s="5" t="n">
         <v>-0.14</v>
       </c>
@@ -61259,10 +61263,10 @@
         </is>
       </c>
       <c r="F634" s="5" t="n">
-        <v>0.140164</v>
+        <v>-0.140164</v>
       </c>
       <c r="G634" s="5" t="n">
-        <v>0.375245</v>
+        <v>-0.375245</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
@@ -61602,10 +61606,10 @@
         </is>
       </c>
       <c r="E638" s="5" t="n">
-        <v>0.08081199999999999</v>
+        <v>-0.08081199999999999</v>
       </c>
       <c r="F638" s="5" t="n">
-        <v>0.140164</v>
+        <v>-0.140164</v>
       </c>
       <c r="G638" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OGI.xlsx
+++ b/output/pdf_financials_xlsx/OGI.xlsx
@@ -850,19 +850,19 @@
         <v>0.067674</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.165537</v>
+        <v>1.212646</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>2.603041</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>4.467583</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>7.804</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>16.083</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>89.02</v>
@@ -899,13 +899,13 @@
         <v>-0.067674</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.440442</v>
+        <v>-1.487551</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.326187</v>
+        <v>-1.276854</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5.314246</v>
+        <v>0.8466630000000001</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-11.101</v>
@@ -2079,46 +2079,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.172404</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.320596</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.15778</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5.726674</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.473694</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>9.857637</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.957</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>55.064</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>55.365</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>68.515</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>33.864</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>106.745</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="35">
@@ -2177,46 +2177,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.172404</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.320596</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.15778</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5.726674</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.473694</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>22.775</v>
+        <v>32.632637</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>32</v>
+        <v>33.957</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>75</v>
+        <v>130.064</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>50.128</v>
+        <v>74.72799999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>128.19</v>
+        <v>183.555</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>30.092</v>
+        <v>98.607</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>33.864</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.821</v>
+        <v>107.566</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.826</v>
+        <v>29.026</v>
       </c>
     </row>
     <row r="37">
@@ -2765,46 +2765,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.172404</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.320596</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.15778</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.008883</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.85669</v>
+        <v>1.382996</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>12.37424</v>
+        <v>2.516603</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.968</v>
+        <v>4.011</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>79.509</v>
+        <v>24.445</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>36.735</v>
+        <v>12.135</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>53.409</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>94.845</v>
+        <v>26.33</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>62.221</v>
+        <v>28.357</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>156.894</v>
+        <v>50.149</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>113.189</v>
+        <v>84.989</v>
       </c>
     </row>
     <row r="49">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -21306,7 +21306,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
@@ -56774,7 +56774,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">

--- a/output/pdf_financials_xlsx/OGI.xlsx
+++ b/output/pdf_financials_xlsx/OGI.xlsx
@@ -1454,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-0.076</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-1.611</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>21.035</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>43.862</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0</v>
+        <v>27.457</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>32.655</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>63.585</v>
       </c>
     </row>
     <row r="38">
@@ -2409,10 +2409,10 @@
         <v>30.157</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.802</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="41">
@@ -2452,7 +2452,7 @@
         <v>42.32</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>46.372</v>
+        <v>90.23399999999999</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>30.157</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>26.33</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>28.357</v>
@@ -3194,16 +3194,16 @@
         <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>2.535937</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>10.056178</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>14.473</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>48.002</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
@@ -3243,16 +3243,16 @@
         <v>0</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.058451</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.472802</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>1.258</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>2.656</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.043031</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -3960,10 +3960,10 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>3.551</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>3.344</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
@@ -4009,10 +4009,10 @@
         <v>0.08</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.076</v>
+        <v>3.627</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>3.344</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0</v>
@@ -4205,10 +4205,10 @@
         <v>14.341</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2.348</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>6.225</v>
+        <v>2.881</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>36.912</v>
@@ -4464,10 +4464,10 @@
         <v>0.0004625456148707431</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.000570643870364439</v>
+        <v>0.01364391086174588</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>8.170228341541689e-05</v>
+        <v>0.01101019971306158</v>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>0.8466630000000001</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>-10.813</v>
+        <v>-10.889</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>22.124</v>
+        <v>20.513</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-136.157</v>
@@ -6208,28 +6208,28 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>26.775</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>131.2</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>50.072</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>113.098</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>40.476</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="116">
@@ -6263,22 +6263,22 @@
         <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-1.43</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.538</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-1.286</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.607</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
     </row>
     <row r="117">
@@ -6487,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.0016</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -10070,7 +10070,11 @@
           <t>Intangible assets and goodwill (Note 8)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -10928,7 +10932,11 @@
           <t>Lease liabilities (Note 14)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -11610,7 +11618,11 @@
           <t>Intangible assets and goodwill (Note 9)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -13074,7 +13086,11 @@
           <t>Intangible assets and goodwill (Note 9 and Note 27)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -14360,7 +14376,11 @@
           <t>Intangible assets and goodwill (Note 10)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -24514,7 +24534,11 @@
           <t>Proceeds from short-term investments</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -25004,7 +25028,11 @@
           <t>Purchase of intangible assets (Note 9)</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -27826,7 +27854,11 @@
           <t>Purchase of intangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -29932,7 +29964,11 @@
           <t>Proceeds from short-term investments (Note 4)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -33338,7 +33374,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -34110,7 +34150,11 @@
           <t>Purchase of intangible assets (Note 10)</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -34194,11 +34238,7 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -35808,7 +35848,11 @@
           <t>Proceeds from share issuance (Note 12)</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -36756,7 +36800,11 @@
           <t>Proceeds from short-term investments</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -40754,7 +40802,11 @@
           <t>Shares issued in private placement</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -42028,7 +42080,11 @@
           <t>Shares issued in private placement</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -44192,7 +44248,11 @@
           <t>Shares issued in the private placement 7,534,391</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -45950,7 +46010,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -57364,7 +57428,11 @@
           <t>Loss from discontinued operations (Note 24)</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
           <t>-</t>
